--- a/data/satech_dun_field_log_sample.xlsx
+++ b/data/satech_dun_field_log_sample.xlsx
@@ -3869,7 +3869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="19" min="1" max="1"/>
@@ -4632,6 +4632,249 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="35" t="inlineStr">
+        <is>
+          <t>start_hello</t>
+        </is>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>Hi {name}! Today is {date}.</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>Hola {name}! Avui és {date}.</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>¡Hola {name}! Hoy es {date}.</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>Привет, {name}! Сегодня {date}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>start_parcels</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>🌱 Your parcels (DUN {campaign}):</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>🌱 Les teves parcel·les (DUN {campaign}):</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>🌱 Tus parcelas (DUN {campaign}):</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>🌱 Ваши участки (DUN {campaign}):</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>start_today</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>Logged today: {n} records.</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>Registrat avui: {n} registres.</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>Registrado hoy: {n} registros.</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>Сегодня записано: {n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>start_functions</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>What I can do:</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>Què puc fer:</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>Qué puedo hacer:</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
+        <is>
+          <t>Что я умею:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>func_voice</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>🎤 Send a voice note about your work — I turn it into a record</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
+        <is>
+          <t>🎤 Envia una nota de veu sobre la feina — la converteixo en un registre</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>🎤 Envía una nota de voz sobre tu trabajo — la convierto en un registro</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>🎤 Отправьте голосовое о работе — я превращу его в запись</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>func_confirm</t>
+        </is>
+      </c>
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>✅ Check the card and confirm, or ✏️ say what to fix</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="inlineStr">
+        <is>
+          <t>✅ Revisa la fitxa i confirma, o ✏️ digues què cal corregir</t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t>✅ Revisa la ficha y confirma, o ✏️ di qué hay que corregir</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="inlineStr">
+        <is>
+          <t>✅ Проверьте карточку и подтвердите или ✏️ скажите, что исправить</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>func_report</t>
+        </is>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>📊 /report — your field log as Excel</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="inlineStr">
+        <is>
+          <t>📊 /report — el teu quadern de camp en Excel</t>
+        </is>
+      </c>
+      <c r="D35" s="35" t="inlineStr">
+        <is>
+          <t>📊 /report — tu cuaderno de campo en Excel</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="inlineStr">
+        <is>
+          <t>📊 /report — журнал работ в Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>func_help</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>❓ /help — show this message again</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>❓ /help — torna a mostrar aquest missatge</t>
+        </is>
+      </c>
+      <c r="D36" s="35" t="inlineStr">
+        <is>
+          <t>❓ /help — vuelve a mostrar este mensaje</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="inlineStr">
+        <is>
+          <t>❓ /help — показать это сообщение снова</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>start_example</t>
+        </is>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>Try: “Today I watered parcel 2, 120 cubic metres.”</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="inlineStr">
+        <is>
+          <t>Prova: «Avui he regat la parcel·la 2, 120 metres cúbics.»</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>Prueba: «Hoy he regado la parcela 2, 120 metros cúbicos.»</t>
+        </is>
+      </c>
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>Например: «Сегодня полил второй участок, 120 кубометров».</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/satech_dun_field_log_sample.xlsx
+++ b/data/satech_dun_field_log_sample.xlsx
@@ -3869,7 +3869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="19" min="1" max="1"/>
@@ -4875,6 +4875,357 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>func_newplot</t>
+        </is>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>🌱 /newplot — add a new plot (or start with “new plot: …”)</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>🌱 /newplot — afegeix una parcel·la nova (o comença amb «nova parcel·la: …»)</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>🌱 /newplot — añade una parcela nueva (o empieza con «nueva parcela: …»)</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>🌱 /newplot — добавить новый участок (или начните с «новый участок: …»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>newplot_ask</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Describe the new plot: what you call it, the crop and its size in hectares. For example: “The cherry trees, cherry, 1.5 hectares, irrigated.”</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>Descriu la parcel·la nova: com l'anomenes, el cultiu i la superfície en hectàrees. Per exemple: «Els cirerers, cirerer, 1,5 hectàrees, de regadiu.»</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>Describe la parcela nueva: cómo la llamas, el cultivo y la superficie en hectáreas. Por ejemplo: «Los cerezos, cerezo, 1,5 hectáreas, de regadío.»</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>Опишите новый участок: как вы его называете, культура и площадь в гектарах. Например: «Вишнёвый сад, вишня, 1,5 гектара, орошаемый».</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>newplot_title</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>New plot</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>Parcel·la nova</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>Parcela nueva</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>Новый участок</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>plot_names</t>
+        </is>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>variety</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>Variety</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="inlineStr">
+        <is>
+          <t>Varietat</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>Variedad</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="inlineStr">
+        <is>
+          <t>Сорт</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>plot_irrigation</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>Irrigation</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>Riego</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="inlineStr">
+        <is>
+          <t>Полив</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t>irrigated</t>
+        </is>
+      </c>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>irrigated</t>
+        </is>
+      </c>
+      <c r="C44" s="35" t="inlineStr">
+        <is>
+          <t>regadiu</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>regadío</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="inlineStr">
+        <is>
+          <t>орошаемый</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>dryland</t>
+        </is>
+      </c>
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>dryland</t>
+        </is>
+      </c>
+      <c r="C45" s="35" t="inlineStr">
+        <is>
+          <t>secà</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>secano</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
+        <is>
+          <t>богарный</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>new_crop</t>
+        </is>
+      </c>
+      <c r="B46" s="35" t="inlineStr">
+        <is>
+          <t>new crop</t>
+        </is>
+      </c>
+      <c r="C46" s="35" t="inlineStr">
+        <is>
+          <t>cultiu nou</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>cultivo nuevo</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="inlineStr">
+        <is>
+          <t>новая культура</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>newplot_missing</t>
+        </is>
+      </c>
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>I still need: {fields}.</t>
+        </is>
+      </c>
+      <c r="C47" s="35" t="inlineStr">
+        <is>
+          <t>Encara em falta: {fields}.</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="inlineStr">
+        <is>
+          <t>Aún me falta: {fields}.</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="inlineStr">
+        <is>
+          <t>Ещё нужно: {fields}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>newplot_incomplete</t>
+        </is>
+      </c>
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>I couldn't get the name, crop and size of the plot. Send /newplot and try again.</t>
+        </is>
+      </c>
+      <c r="C48" s="35" t="inlineStr">
+        <is>
+          <t>No he pogut obtenir el nom, el cultiu i la superfície de la parcel·la. Envia /newplot i torna-ho a provar.</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="inlineStr">
+        <is>
+          <t>No he podido obtener el nombre, el cultivo y la superficie de la parcela. Envía /newplot e inténtalo de nuevo.</t>
+        </is>
+      </c>
+      <c r="E48" s="35" t="inlineStr">
+        <is>
+          <t>Не удалось получить название, культуру и площадь участка. Отправьте /newplot и попробуйте снова.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t>newplot_saved</t>
+        </is>
+      </c>
+      <c r="B49" s="35" t="inlineStr">
+        <is>
+          <t>Plot {alias} added. You can log work on it now.</t>
+        </is>
+      </c>
+      <c r="C49" s="35" t="inlineStr">
+        <is>
+          <t>Parcel·la {alias} afegida. Ja hi pots registrar feines.</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="inlineStr">
+        <is>
+          <t>Parcela {alias} añadida. Ya puedes registrar trabajos en ella.</t>
+        </is>
+      </c>
+      <c r="E49" s="35" t="inlineStr">
+        <is>
+          <t>Участок {alias} добавлен. Теперь можно записывать работы на нём.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>newplot_name_taken</t>
+        </is>
+      </c>
+      <c r="B50" s="35" t="inlineStr">
+        <is>
+          <t>“{name}” is already the name of {alias}. Send /newplot again with another name.</t>
+        </is>
+      </c>
+      <c r="C50" s="35" t="inlineStr">
+        <is>
+          <t>«{name}» ja és el nom de {alias}. Envia /newplot de nou amb un altre nom.</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="inlineStr">
+        <is>
+          <t>«{name}» ya es el nombre de {alias}. Envía /newplot de nuevo con otro nombre.</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
+        <is>
+          <t>«{name}» — уже название участка {alias}. Отправьте /newplot снова с другим названием.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
